--- a/output/pdf_financials_xlsx/ACDX.xlsx
+++ b/output/pdf_financials_xlsx/ACDX.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.120656</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02398</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005178</v>
       </c>
     </row>
     <row r="13">
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.103682</v>
+        <v>-1.224338</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-17.569606</v>
+        <v>-17.593586</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.260715</v>
+        <v>-0.265893</v>
       </c>
     </row>
     <row r="28">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.103682</v>
+        <v>-1.224338</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-17.569606</v>
+        <v>-17.593586</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.260715</v>
+        <v>-0.265893</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.523045</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.100428</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.594489</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.523045</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.100428</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.594489</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.557102</v>
+        <v>0.034057</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.102184</v>
+        <v>0.001756</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.619431</v>
+        <v>0.024942</v>
       </c>
     </row>
     <row r="49">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
